--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110825</v>
+        <v>121110924</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573029</v>
+        <v>572975</v>
       </c>
       <c r="R2" t="n">
-        <v>6511869</v>
+        <v>6511846</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110787</v>
+        <v>121111274</v>
       </c>
       <c r="B3" t="n">
-        <v>91963</v>
+        <v>94747</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573029</v>
+        <v>572986</v>
       </c>
       <c r="R3" t="n">
-        <v>6511869</v>
+        <v>6511972</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111291</v>
+        <v>121110787</v>
       </c>
       <c r="B4" t="n">
-        <v>79216</v>
+        <v>91973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572986</v>
+        <v>573029</v>
       </c>
       <c r="R4" t="n">
-        <v>6511972</v>
+        <v>6511869</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111789</v>
+        <v>121110825</v>
       </c>
       <c r="B5" t="n">
-        <v>105176</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573019</v>
+        <v>573029</v>
       </c>
       <c r="R5" t="n">
-        <v>6512198</v>
+        <v>6511869</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111274</v>
+        <v>121111789</v>
       </c>
       <c r="B6" t="n">
-        <v>94737</v>
+        <v>105186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,37 +1099,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572986</v>
+        <v>573019</v>
       </c>
       <c r="R6" t="n">
-        <v>6511972</v>
+        <v>6512198</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110924</v>
+        <v>121111735</v>
       </c>
       <c r="B7" t="n">
-        <v>91963</v>
+        <v>90717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,38 +1206,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572975</v>
+        <v>573002</v>
       </c>
       <c r="R7" t="n">
-        <v>6511846</v>
+        <v>6512194</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111746</v>
+        <v>121111291</v>
       </c>
       <c r="B8" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572987</v>
+        <v>572986</v>
       </c>
       <c r="R8" t="n">
-        <v>6512184</v>
+        <v>6511972</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121111735</v>
+        <v>121111746</v>
       </c>
       <c r="B9" t="n">
-        <v>90707</v>
+        <v>79219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573002</v>
+        <v>572987</v>
       </c>
       <c r="R9" t="n">
-        <v>6512194</v>
+        <v>6512184</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121109638</v>
+        <v>121109977</v>
       </c>
       <c r="B10" t="n">
-        <v>94737</v>
+        <v>94854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121109728</v>
+        <v>121109638</v>
       </c>
       <c r="B11" t="n">
-        <v>105176</v>
+        <v>94747</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,33 +1618,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -1713,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121109438</v>
+        <v>121109120</v>
       </c>
       <c r="B12" t="n">
-        <v>79216</v>
+        <v>78246</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,34 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573148</v>
+        <v>573235</v>
       </c>
       <c r="R12" t="n">
-        <v>6512015</v>
+        <v>6512054</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1815,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121109977</v>
+        <v>121109728</v>
       </c>
       <c r="B13" t="n">
-        <v>94844</v>
+        <v>105186</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,24 +1822,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121109120</v>
+        <v>121109438</v>
       </c>
       <c r="B14" t="n">
-        <v>78243</v>
+        <v>79219</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,34 +1933,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573235</v>
+        <v>573148</v>
       </c>
       <c r="R14" t="n">
-        <v>6512054</v>
+        <v>6512015</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121144820</v>
+        <v>121144935</v>
       </c>
       <c r="B15" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573204</v>
+        <v>573186</v>
       </c>
       <c r="R15" t="n">
-        <v>6512051</v>
+        <v>6512003</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121144935</v>
+        <v>121145003</v>
       </c>
       <c r="B16" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,14 +2157,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573186</v>
+        <v>573145</v>
       </c>
       <c r="R16" t="n">
-        <v>6512003</v>
+        <v>6512018</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121144882</v>
+        <v>121144820</v>
       </c>
       <c r="B17" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573192</v>
+        <v>573204</v>
       </c>
       <c r="R17" t="n">
-        <v>6512035</v>
+        <v>6512051</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2325,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121145003</v>
+        <v>121144882</v>
       </c>
       <c r="B18" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,14 +2361,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573145</v>
+        <v>573192</v>
       </c>
       <c r="R18" t="n">
-        <v>6512018</v>
+        <v>6512035</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110924</v>
+        <v>121111274</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>94747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572975</v>
+        <v>572986</v>
       </c>
       <c r="R2" t="n">
-        <v>6511846</v>
+        <v>6511972</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111274</v>
+        <v>121110924</v>
       </c>
       <c r="B3" t="n">
-        <v>94747</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572986</v>
+        <v>572975</v>
       </c>
       <c r="R3" t="n">
-        <v>6511972</v>
+        <v>6511846</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111274</v>
+        <v>121110924</v>
       </c>
       <c r="B2" t="n">
-        <v>94747</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572986</v>
+        <v>572975</v>
       </c>
       <c r="R2" t="n">
-        <v>6511972</v>
+        <v>6511846</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110924</v>
+        <v>121111274</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
+        <v>94747</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572975</v>
+        <v>572986</v>
       </c>
       <c r="R3" t="n">
-        <v>6511846</v>
+        <v>6511972</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110924</v>
+        <v>121111746</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572975</v>
+        <v>572987</v>
       </c>
       <c r="R2" t="n">
-        <v>6511846</v>
+        <v>6512184</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111274</v>
+        <v>121110924</v>
       </c>
       <c r="B3" t="n">
-        <v>94747</v>
+        <v>91973</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572986</v>
+        <v>572975</v>
       </c>
       <c r="R3" t="n">
-        <v>6511972</v>
+        <v>6511846</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121110825</v>
+        <v>121111789</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>105186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573029</v>
+        <v>573019</v>
       </c>
       <c r="R5" t="n">
-        <v>6511869</v>
+        <v>6512198</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111789</v>
+        <v>121111291</v>
       </c>
       <c r="B6" t="n">
-        <v>105186</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,50 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573019</v>
+        <v>572986</v>
       </c>
       <c r="R6" t="n">
-        <v>6512198</v>
+        <v>6511972</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121111735</v>
+        <v>121111229</v>
       </c>
       <c r="B7" t="n">
-        <v>90717</v>
+        <v>94747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573002</v>
+        <v>572986</v>
       </c>
       <c r="R7" t="n">
-        <v>6512194</v>
+        <v>6511972</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111291</v>
+        <v>121111735</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>90717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572986</v>
+        <v>573002</v>
       </c>
       <c r="R8" t="n">
-        <v>6511972</v>
+        <v>6512194</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121111746</v>
+        <v>121110825</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>92008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,37 +1414,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572987</v>
+        <v>573029</v>
       </c>
       <c r="R9" t="n">
-        <v>6512184</v>
+        <v>6511869</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121109638</v>
+        <v>121109728</v>
       </c>
       <c r="B11" t="n">
-        <v>94747</v>
+        <v>105186</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,24 +1618,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -1704,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121109120</v>
+        <v>121109438</v>
       </c>
       <c r="B12" t="n">
-        <v>78246</v>
+        <v>79219</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,34 +1729,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573235</v>
+        <v>573148</v>
       </c>
       <c r="R12" t="n">
-        <v>6512054</v>
+        <v>6512015</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1806,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121109728</v>
+        <v>121109638</v>
       </c>
       <c r="B13" t="n">
-        <v>105186</v>
+        <v>94747</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,33 +1831,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121109438</v>
+        <v>121109120</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>78246</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,34 +1933,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573148</v>
+        <v>573235</v>
       </c>
       <c r="R14" t="n">
-        <v>6512015</v>
+        <v>6512054</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121144935</v>
+        <v>121144882</v>
       </c>
       <c r="B15" t="n">
         <v>79219</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573186</v>
+        <v>573192</v>
       </c>
       <c r="R15" t="n">
-        <v>6512003</v>
+        <v>6512035</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121144820</v>
+        <v>121144935</v>
       </c>
       <c r="B17" t="n">
         <v>79219</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573204</v>
+        <v>573186</v>
       </c>
       <c r="R17" t="n">
-        <v>6512051</v>
+        <v>6512003</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121144882</v>
+        <v>121144820</v>
       </c>
       <c r="B18" t="n">
         <v>79219</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573192</v>
+        <v>573204</v>
       </c>
       <c r="R18" t="n">
-        <v>6512035</v>
+        <v>6512051</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111746</v>
+        <v>121111789</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>105199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572987</v>
+        <v>573019</v>
       </c>
       <c r="R2" t="n">
-        <v>6512184</v>
+        <v>6512198</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110924</v>
+        <v>121110825</v>
       </c>
       <c r="B3" t="n">
-        <v>91973</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572975</v>
+        <v>573029</v>
       </c>
       <c r="R3" t="n">
-        <v>6511846</v>
+        <v>6511869</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +891,7 @@
         <v>121110787</v>
       </c>
       <c r="B4" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111789</v>
+        <v>121111746</v>
       </c>
       <c r="B5" t="n">
-        <v>105186</v>
+        <v>79222</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,50 +1002,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573019</v>
+        <v>572987</v>
       </c>
       <c r="R5" t="n">
-        <v>6512198</v>
+        <v>6512184</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111291</v>
+        <v>121111274</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>94759</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121111229</v>
+        <v>121111291</v>
       </c>
       <c r="B7" t="n">
-        <v>94747</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
         <v>121111735</v>
       </c>
       <c r="B8" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121110825</v>
+        <v>121110924</v>
       </c>
       <c r="B9" t="n">
-        <v>92008</v>
+        <v>91985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573029</v>
+        <v>572975</v>
       </c>
       <c r="R9" t="n">
-        <v>6511869</v>
+        <v>6511846</v>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121109977</v>
+        <v>121109438</v>
       </c>
       <c r="B10" t="n">
-        <v>94854</v>
+        <v>79222</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573110</v>
+        <v>573148</v>
       </c>
       <c r="R10" t="n">
-        <v>6511962</v>
+        <v>6512015</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>121109728</v>
       </c>
       <c r="B11" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121109438</v>
+        <v>121109638</v>
       </c>
       <c r="B12" t="n">
-        <v>79219</v>
+        <v>94759</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,25 +1725,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573148</v>
+        <v>573110</v>
       </c>
       <c r="R12" t="n">
-        <v>6512015</v>
+        <v>6511962</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121109638</v>
+        <v>121109977</v>
       </c>
       <c r="B13" t="n">
-        <v>94747</v>
+        <v>94866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1920,7 +1920,7 @@
         <v>121109120</v>
       </c>
       <c r="B14" t="n">
-        <v>78246</v>
+        <v>78249</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>121144882</v>
       </c>
       <c r="B15" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>121145003</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>121144935</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>121144820</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111789</v>
+        <v>121110825</v>
       </c>
       <c r="B2" t="n">
-        <v>105199</v>
+        <v>92021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573019</v>
+        <v>573029</v>
       </c>
       <c r="R2" t="n">
-        <v>6512198</v>
+        <v>6511869</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110825</v>
+        <v>121111229</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>94760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573029</v>
+        <v>572986</v>
       </c>
       <c r="R3" t="n">
-        <v>6511869</v>
+        <v>6511972</v>
       </c>
       <c r="S3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110787</v>
+        <v>121111735</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>90730</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573029</v>
+        <v>573002</v>
       </c>
       <c r="R4" t="n">
-        <v>6511869</v>
+        <v>6512194</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111746</v>
+        <v>121110924</v>
       </c>
       <c r="B5" t="n">
-        <v>79222</v>
+        <v>91986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572987</v>
+        <v>572975</v>
       </c>
       <c r="R5" t="n">
-        <v>6512184</v>
+        <v>6511846</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111274</v>
+        <v>121110787</v>
       </c>
       <c r="B6" t="n">
-        <v>94759</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572986</v>
+        <v>573029</v>
       </c>
       <c r="R6" t="n">
-        <v>6511972</v>
+        <v>6511869</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121111291</v>
+        <v>121111746</v>
       </c>
       <c r="B7" t="n">
         <v>79222</v>
@@ -1234,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572986</v>
+        <v>572987</v>
       </c>
       <c r="R7" t="n">
-        <v>6511972</v>
+        <v>6512184</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1296,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111735</v>
+        <v>121111789</v>
       </c>
       <c r="B8" t="n">
-        <v>90729</v>
+        <v>105200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,41 +1299,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573002</v>
+        <v>573019</v>
       </c>
       <c r="R8" t="n">
-        <v>6512194</v>
+        <v>6512198</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121110924</v>
+        <v>121111291</v>
       </c>
       <c r="B9" t="n">
-        <v>91985</v>
+        <v>79222</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,38 +1410,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572975</v>
+        <v>572986</v>
       </c>
       <c r="R9" t="n">
-        <v>6511846</v>
+        <v>6511972</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121109438</v>
+        <v>121109977</v>
       </c>
       <c r="B10" t="n">
-        <v>79222</v>
+        <v>94867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573148</v>
+        <v>573110</v>
       </c>
       <c r="R10" t="n">
-        <v>6512015</v>
+        <v>6511962</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121109728</v>
+        <v>121109120</v>
       </c>
       <c r="B11" t="n">
-        <v>105199</v>
+        <v>78249</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,50 +1614,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573110</v>
+        <v>573235</v>
       </c>
       <c r="R11" t="n">
-        <v>6511962</v>
+        <v>6512054</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,7 +1707,7 @@
         <v>121109638</v>
       </c>
       <c r="B12" t="n">
-        <v>94759</v>
+        <v>94760</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121109977</v>
+        <v>121109438</v>
       </c>
       <c r="B13" t="n">
-        <v>94866</v>
+        <v>79222</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,13 +1846,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573110</v>
+        <v>573148</v>
       </c>
       <c r="R13" t="n">
-        <v>6511962</v>
+        <v>6512015</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121109120</v>
+        <v>121109728</v>
       </c>
       <c r="B14" t="n">
-        <v>78249</v>
+        <v>105200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,41 +1920,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573235</v>
+        <v>573110</v>
       </c>
       <c r="R14" t="n">
-        <v>6512054</v>
+        <v>6511962</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121144882</v>
+        <v>121144970</v>
       </c>
       <c r="B15" t="n">
         <v>79222</v>
@@ -2055,14 +2055,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573192</v>
+        <v>573145</v>
       </c>
       <c r="R15" t="n">
-        <v>6512035</v>
+        <v>6512018</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2121,7 +2121,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121145003</v>
+        <v>121144820</v>
       </c>
       <c r="B16" t="n">
         <v>79222</v>
@@ -2157,14 +2157,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573145</v>
+        <v>573204</v>
       </c>
       <c r="R16" t="n">
-        <v>6512018</v>
+        <v>6512051</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121144935</v>
+        <v>121144882</v>
       </c>
       <c r="B17" t="n">
         <v>79222</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573186</v>
+        <v>573192</v>
       </c>
       <c r="R17" t="n">
-        <v>6512003</v>
+        <v>6512035</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121144820</v>
+        <v>121144935</v>
       </c>
       <c r="B18" t="n">
         <v>79222</v>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573204</v>
+        <v>573186</v>
       </c>
       <c r="R18" t="n">
-        <v>6512051</v>
+        <v>6512003</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110825</v>
+        <v>121110924</v>
       </c>
       <c r="B2" t="n">
-        <v>92021</v>
+        <v>91989</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573029</v>
+        <v>572975</v>
       </c>
       <c r="R2" t="n">
-        <v>6511869</v>
+        <v>6511846</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111229</v>
+        <v>121111274</v>
       </c>
       <c r="B3" t="n">
-        <v>94760</v>
+        <v>94763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111735</v>
+        <v>121111746</v>
       </c>
       <c r="B4" t="n">
-        <v>90730</v>
+        <v>79225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573002</v>
+        <v>572987</v>
       </c>
       <c r="R4" t="n">
-        <v>6512194</v>
+        <v>6512184</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121110924</v>
+        <v>121110787</v>
       </c>
       <c r="B5" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572975</v>
+        <v>573029</v>
       </c>
       <c r="R5" t="n">
-        <v>6511846</v>
+        <v>6511869</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121110787</v>
+        <v>121111735</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>90733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573029</v>
+        <v>573002</v>
       </c>
       <c r="R6" t="n">
-        <v>6511869</v>
+        <v>6512194</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121111746</v>
+        <v>121110825</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>92024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572987</v>
+        <v>573029</v>
       </c>
       <c r="R7" t="n">
-        <v>6512184</v>
+        <v>6511869</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>121111789</v>
       </c>
       <c r="B8" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>121111291</v>
       </c>
       <c r="B9" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>121109977</v>
       </c>
       <c r="B10" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121109120</v>
+        <v>121109438</v>
       </c>
       <c r="B11" t="n">
-        <v>78249</v>
+        <v>79225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,34 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573235</v>
+        <v>573148</v>
       </c>
       <c r="R11" t="n">
-        <v>6512054</v>
+        <v>6512015</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1707,7 +1707,7 @@
         <v>121109638</v>
       </c>
       <c r="B12" t="n">
-        <v>94760</v>
+        <v>94763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121109438</v>
+        <v>121109120</v>
       </c>
       <c r="B13" t="n">
-        <v>79222</v>
+        <v>78252</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,34 +1822,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573148</v>
+        <v>573235</v>
       </c>
       <c r="R13" t="n">
-        <v>6512015</v>
+        <v>6512054</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1911,7 +1911,7 @@
         <v>121109728</v>
       </c>
       <c r="B14" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121144970</v>
+        <v>121144882</v>
       </c>
       <c r="B15" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,14 +2055,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573145</v>
+        <v>573192</v>
       </c>
       <c r="R15" t="n">
-        <v>6512018</v>
+        <v>6512035</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2124,7 +2124,7 @@
         <v>121144820</v>
       </c>
       <c r="B16" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121144882</v>
+        <v>121144970</v>
       </c>
       <c r="B17" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2259,14 +2259,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573192</v>
+        <v>573145</v>
       </c>
       <c r="R17" t="n">
-        <v>6512035</v>
+        <v>6512018</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2328,7 +2328,7 @@
         <v>121144935</v>
       </c>
       <c r="B18" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 43298-2024 artfynd.xlsx
+++ b/artfynd/A 43298-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111274</v>
+        <v>121110825</v>
       </c>
       <c r="B3" t="n">
-        <v>94763</v>
+        <v>92024</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572986</v>
+        <v>573029</v>
       </c>
       <c r="R3" t="n">
-        <v>6511972</v>
+        <v>6511869</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111746</v>
+        <v>121111229</v>
       </c>
       <c r="B4" t="n">
-        <v>79225</v>
+        <v>94763</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572987</v>
+        <v>572986</v>
       </c>
       <c r="R4" t="n">
-        <v>6512184</v>
+        <v>6511972</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121110787</v>
+        <v>121111746</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>79225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573029</v>
+        <v>572987</v>
       </c>
       <c r="R5" t="n">
-        <v>6511869</v>
+        <v>6512184</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111735</v>
+        <v>121110787</v>
       </c>
       <c r="B6" t="n">
-        <v>90733</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Norrköping, Norrköping, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573002</v>
+        <v>573029</v>
       </c>
       <c r="R6" t="n">
-        <v>6512194</v>
+        <v>6511869</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110825</v>
+        <v>121111735</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>90733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrköping, Norrköping, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573029</v>
+        <v>573002</v>
       </c>
       <c r="R7" t="n">
-        <v>6511869</v>
+        <v>6512194</v>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121109977</v>
+        <v>121109438</v>
       </c>
       <c r="B10" t="n">
-        <v>94870</v>
+        <v>79225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,13 +1540,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573110</v>
+        <v>573148</v>
       </c>
       <c r="R10" t="n">
-        <v>6511962</v>
+        <v>6512015</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121109438</v>
+        <v>121109120</v>
       </c>
       <c r="B11" t="n">
-        <v>79225</v>
+        <v>78252</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,34 +1618,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bockmossen, Bockmossen, Ög</t>
+          <t>Ämtefall, Ämtefall, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573148</v>
+        <v>573235</v>
       </c>
       <c r="R11" t="n">
-        <v>6512015</v>
+        <v>6512054</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121109638</v>
+        <v>121109977</v>
       </c>
       <c r="B12" t="n">
-        <v>94763</v>
+        <v>94870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121109120</v>
+        <v>121109728</v>
       </c>
       <c r="B13" t="n">
-        <v>78252</v>
+        <v>105203</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,41 +1818,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ämtefall, Ämtefall, Ög</t>
+          <t>Bockmossen, Bockmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573235</v>
+        <v>573110</v>
       </c>
       <c r="R13" t="n">
-        <v>6512054</v>
+        <v>6511962</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121109728</v>
+        <v>121109638</v>
       </c>
       <c r="B14" t="n">
-        <v>105203</v>
+        <v>94763</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,33 +1933,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bockmossen, Bockmossen, Ög</t>
